--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>15157105</v>
       </c>
       <c r="B2" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506826.3856642735</v>
+        <v>506826</v>
       </c>
       <c r="R2" t="n">
-        <v>6531569.934609653</v>
+        <v>6531570</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,8 +813,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15157105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,67 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15157105</v>
+        <v>135611313</v>
       </c>
       <c r="B2" t="n">
-        <v>45049</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gålsjö 3750/0450, Nrk</t>
+          <t>djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506826</v>
+        <v>506687</v>
       </c>
       <c r="R2" t="n">
-        <v>6531570</v>
+        <v>6531532</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,27 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På Knautia</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,24 +785,160 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135611313</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15157105</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gålsjö 3750/0450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506826</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6531570</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15157105</t>
         </is>
@@ -822,6 +947,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135611313</v>
+        <v>135531568</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506687</v>
+        <v>506812</v>
       </c>
       <c r="R2" t="n">
-        <v>6531532</v>
+        <v>6531589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack Gammal stor tall Märkt no 19 av Skogsförvaltaren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,73 +799,62 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135611313</t>
+          <t>https://artportalen.se/Sighting/135531568</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15157105</v>
+        <v>135611313</v>
       </c>
       <c r="B3" t="n">
-        <v>45049</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gålsjö 3750/0450, Nrk</t>
+          <t>djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506826</v>
+        <v>506687</v>
       </c>
       <c r="R3" t="n">
-        <v>6531570</v>
+        <v>6531532</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,27 +878,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På Knautia</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,24 +910,160 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135611313</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>15157105</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gålsjö 3750/0450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506826</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6531570</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15157105</t>
         </is>
@@ -948,6 +1073,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,67 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15157105</v>
+        <v>135531568</v>
       </c>
       <c r="B2" t="n">
-        <v>45049</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gålsjö 3750/0450, Nrk</t>
+          <t>djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506826</v>
+        <v>506812</v>
       </c>
       <c r="R2" t="n">
-        <v>6531570</v>
+        <v>6531589</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,27 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På Knautia</t>
+          <t>Färska ringhack Gammal stor tall Märkt no 19 av Skogsförvaltaren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,24 +785,285 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531568</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135611313</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>djupsjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506687</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6531532</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135611313</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>15157105</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gålsjö 3750/0450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506826</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6531570</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15157105</t>
         </is>
@@ -822,6 +1072,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,67 +930,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15157105</v>
+        <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>45049</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gålsjö 3750/0450, Nrk</t>
+          <t>djupsjön, djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506826</v>
+        <v>506607</v>
       </c>
       <c r="R4" t="n">
-        <v>6531570</v>
+        <v>6531633</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,27 +995,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Knautia</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,24 +1022,160 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135928580</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>15157105</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gålsjö 3750/0450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506826</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6531570</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15157105</t>
         </is>
@@ -1074,6 +1186,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135531568</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135611313</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>135611313</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18246-2026 artfynd.xlsx
+++ b/artfynd/A 18246-2026 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>135928580</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
